--- a/results/qwen3_5_9b/comparison_CoTRAG/CoTRAG_evaluated.xlsx
+++ b/results/qwen3_5_9b/comparison_CoTRAG/CoTRAG_evaluated.xlsx
@@ -505,35 +505,37 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.01005025067144773</v>
+        <v>0.2522522473789105</v>
       </c>
       <c r="D2" t="n">
-        <v>4.112145644782141e-255</v>
+        <v>3.499347156910729e-155</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3551344275474548</v>
+        <v>0.6088988780975342</v>
       </c>
       <c r="F2" t="n">
-        <v>18.17750000000001</v>
+        <v>39.61143670886079</v>
       </c>
       <c r="G2" t="n">
-        <v>0.07757805108798486</v>
+        <v>0.7880794701986755</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
       <c r="K2" t="n">
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2</v>
+        <v>0.2377049180327869</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.3464052287581699</v>
       </c>
     </row>
     <row r="3">
@@ -546,35 +548,37 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>0.1111111091358025</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>8.493666525496109e-232</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4478027522563934</v>
+        <v>0.5002129077911377</v>
       </c>
       <c r="F3" t="n">
-        <v>18.17750000000001</v>
+        <v>23.25551702395967</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7522935779816514</v>
+        <v>4.651376146788991</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
       <c r="K3" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2</v>
+        <v>0.3382352941176471</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2546583850931677</v>
       </c>
     </row>
     <row r="4">
@@ -587,35 +591,37 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>0.1984126936961452</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>2.210547689163357e-79</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2987848222255707</v>
+        <v>0.5246517658233643</v>
       </c>
       <c r="F4" t="n">
-        <v>18.17750000000001</v>
+        <v>43.48427083333334</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0876068376068376</v>
+        <v>0.5908119658119658</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
       </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
       <c r="K4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2</v>
+        <v>0.375</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.3670886075949367</v>
       </c>
     </row>
     <row r="5">
@@ -628,35 +634,37 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>0.2399999952880001</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>4.67801905661789e-79</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2985583543777466</v>
+        <v>0.6336413621902466</v>
       </c>
       <c r="F5" t="n">
-        <v>18.17750000000001</v>
+        <v>38.72775682837343</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06710310965630115</v>
+        <v>0.6235679214402619</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
       </c>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
       <c r="K5" t="n">
         <v>0.5</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2</v>
+        <v>0.3663366336633663</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.5121951219512195</v>
       </c>
     </row>
     <row r="6">
@@ -669,35 +677,37 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.01265822711744917</v>
+        <v>0.2421524620273885</v>
       </c>
       <c r="D6" t="n">
-        <v>6.490056534318242e-251</v>
+        <v>0.0083955954548054</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3351855278015137</v>
+        <v>0.5851066112518311</v>
       </c>
       <c r="F6" t="n">
-        <v>18.17750000000001</v>
+        <v>53.62264705882353</v>
       </c>
       <c r="G6" t="n">
-        <v>0.09425287356321839</v>
+        <v>0.4804597701149425</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
       </c>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
       <c r="K6" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="7">
@@ -710,35 +720,37 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.004024144630681487</v>
+        <v>0.3474452514143961</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>0.007698327232697096</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3596178889274597</v>
+        <v>0.6456795930862427</v>
       </c>
       <c r="F7" t="n">
-        <v>18.17750000000001</v>
+        <v>32.8283071567358</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0238580157113762</v>
+        <v>0.3520512074483561</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.2941176470588235</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
       <c r="K7" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2</v>
+        <v>0.1858974358974359</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2</v>
+        <v>0.7321428571428571</v>
       </c>
     </row>
     <row r="8">
@@ -751,35 +763,37 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>0.1627118608960644</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>2.393744328776576e-157</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3447666764259338</v>
+        <v>0.5901678204536438</v>
       </c>
       <c r="F8" t="n">
-        <v>18.17750000000001</v>
+        <v>26.61927710843375</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05694444444444444</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
       <c r="K8" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M8" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.1538461538461539</v>
       </c>
     </row>
     <row r="9">
@@ -792,35 +806,37 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.006968640705605289</v>
+        <v>0.2216358800707319</v>
       </c>
       <c r="D9" t="n">
-        <v>1.940725192637606e-274</v>
+        <v>2.352199119576295e-79</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3247340321540833</v>
+        <v>0.642425537109375</v>
       </c>
       <c r="F9" t="n">
-        <v>18.17750000000001</v>
+        <v>52.66048128342248</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04750869061413673</v>
+        <v>0.3771726535341831</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.4375</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
       <c r="K9" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2</v>
+        <v>0.3647058823529412</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.3548387096774193</v>
       </c>
     </row>
     <row r="10">
@@ -833,35 +849,37 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>0.2184154125616607</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>0.03677245973087152</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3366994261741638</v>
+        <v>0.647664487361908</v>
       </c>
       <c r="F10" t="n">
-        <v>18.17750000000001</v>
+        <v>6.092778885703638</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05423280423280423</v>
+        <v>0.9609788359788359</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
       <c r="K10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="M10" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.5358649789029536</v>
       </c>
     </row>
     <row r="11">
@@ -874,35 +892,37 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.006734006338128786</v>
+        <v>0.314855871253337</v>
       </c>
       <c r="D11" t="n">
-        <v>1.427007095027129e-284</v>
+        <v>0.03531317188655015</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3138718605041504</v>
+        <v>0.5857160091400146</v>
       </c>
       <c r="F11" t="n">
-        <v>18.17750000000001</v>
+        <v>57.37569230769233</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0448332422088573</v>
+        <v>0.4980863860032805</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
       </c>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
       <c r="K11" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2</v>
+        <v>0.3257575757575757</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.494949494949495</v>
       </c>
     </row>
     <row r="12">
@@ -915,35 +935,37 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.1949999958201251</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>9.049280421314446e-156</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3342090249061584</v>
+        <v>0.6282260417938232</v>
       </c>
       <c r="F12" t="n">
-        <v>18.17750000000001</v>
+        <v>48.93568181818185</v>
       </c>
       <c r="G12" t="n">
-        <v>0.04669703872437358</v>
+        <v>0.4749430523917996</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2</v>
+        <v>0.2342342342342342</v>
       </c>
       <c r="M12" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.281437125748503</v>
       </c>
     </row>
     <row r="13">
@@ -956,35 +978,37 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.006622516166834812</v>
+        <v>0.169863010632539</v>
       </c>
       <c r="D13" t="n">
-        <v>1.848714805888607e-281</v>
+        <v>1.138729583003279e-80</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3324247598648071</v>
+        <v>0.6448227763175964</v>
       </c>
       <c r="F13" t="n">
-        <v>18.17750000000001</v>
+        <v>59.65907721280604</v>
       </c>
       <c r="G13" t="n">
-        <v>0.04545454545454546</v>
+        <v>0.2361419068736142</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2</v>
+        <v>0.3018867924528302</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2783505154639175</v>
       </c>
     </row>
     <row r="14">
@@ -997,35 +1021,37 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.1792618579192678</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>0.01263108921430186</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3325183093547821</v>
+        <v>0.6010398864746094</v>
       </c>
       <c r="F14" t="n">
-        <v>18.17750000000001</v>
+        <v>2.960311004784728</v>
       </c>
       <c r="G14" t="n">
-        <v>0.04555555555555556</v>
+        <v>0.9288888888888889</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
       <c r="K14" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2</v>
+        <v>0.2023809523809524</v>
       </c>
       <c r="M14" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.5679012345679012</v>
       </c>
     </row>
     <row r="15">
@@ -1038,35 +1064,37 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>0.2782608646502836</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>3.50839260170082e-155</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3425537645816803</v>
+        <v>0.7033020257949829</v>
       </c>
       <c r="F15" t="n">
-        <v>18.17750000000001</v>
+        <v>38.87717922077925</v>
       </c>
       <c r="G15" t="n">
-        <v>0.164989939637827</v>
+        <v>1.702213279678068</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2</v>
+        <v>0.2929292929292929</v>
       </c>
       <c r="M15" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.3469387755102041</v>
       </c>
     </row>
     <row r="16">
@@ -1079,35 +1107,37 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>0.2671480094639576</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>0.06554648452824906</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3363480567932129</v>
+        <v>0.6893495917320251</v>
       </c>
       <c r="F16" t="n">
-        <v>18.17750000000001</v>
+        <v>42.42375920810315</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1169757489300999</v>
+        <v>1.369472182596291</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
       <c r="K16" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2</v>
+        <v>0.2935779816513762</v>
       </c>
       <c r="M16" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.3801652892561983</v>
       </c>
     </row>
     <row r="17">
@@ -1120,35 +1150,37 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.2450142402805173</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>7.644460866191573e-79</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3349585831165314</v>
+        <v>0.6701482534408569</v>
       </c>
       <c r="F17" t="n">
-        <v>18.17750000000001</v>
+        <v>55.32170203359863</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1102150537634409</v>
+        <v>1.827956989247312</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
       <c r="K17" t="n">
         <v>0.5</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2</v>
+        <v>0.2847682119205298</v>
       </c>
       <c r="M17" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.5736434108527132</v>
       </c>
     </row>
     <row r="18">
@@ -1161,35 +1193,37 @@
         </is>
       </c>
       <c r="C18" t="n">
+        <v>0.3116057187144912</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.1019237140176351</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.6736286878585815</v>
+      </c>
+      <c r="F18" t="n">
+        <v>57.00158730158731</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.6304517133956387</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
         <v>0</v>
       </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.3638949990272522</v>
-      </c>
-      <c r="F18" t="n">
-        <v>18.17750000000001</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.03193146417445483</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="n">
-        <v>0.5</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.2</v>
+        <v>0.2611111111111111</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.5780590717299579</v>
       </c>
     </row>
     <row r="19">
@@ -1202,35 +1236,37 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>0.1245901607739856</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>2.274367346849618e-81</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3354047536849976</v>
+        <v>0.6037366986274719</v>
       </c>
       <c r="F19" t="n">
-        <v>18.17750000000001</v>
+        <v>19.49400000000003</v>
       </c>
       <c r="G19" t="n">
-        <v>0.05405405405405406</v>
+        <v>0.2491760052735663</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>0.2352941176470588</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
       <c r="K19" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2</v>
+        <v>0.3018867924528302</v>
       </c>
       <c r="M19" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.1240875912408759</v>
       </c>
     </row>
     <row r="20">
@@ -1243,35 +1279,37 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.007999999531520028</v>
+        <v>0.2670623105438985</v>
       </c>
       <c r="D20" t="n">
-        <v>2.011151139993215e-262</v>
+        <v>3.01248324859832e-79</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3511017560958862</v>
+        <v>0.6838187575340271</v>
       </c>
       <c r="F20" t="n">
-        <v>18.17750000000001</v>
+        <v>55.89562500000002</v>
       </c>
       <c r="G20" t="n">
-        <v>0.05819730305180979</v>
+        <v>0.4109297374024131</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
       <c r="K20" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2</v>
+        <v>0.3291139240506329</v>
       </c>
       <c r="M20" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.2073170731707317</v>
       </c>
     </row>
     <row r="21">
@@ -1284,35 +1322,37 @@
         </is>
       </c>
       <c r="C21" t="n">
+        <v>0.1603665479552675</v>
+      </c>
+      <c r="D21" t="n">
+        <v>7.254289863126926e-79</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.5893725156784058</v>
+      </c>
+      <c r="F21" t="n">
+        <v>30.91215960779397</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.705949008498584</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
         <v>0</v>
       </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.3511861562728882</v>
-      </c>
-      <c r="F21" t="n">
-        <v>18.17750000000001</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.04645892351274788</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="n">
-        <v>0.5</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.2</v>
+        <v>0.1399082568807339</v>
       </c>
       <c r="M21" t="n">
-        <v>0.01408450704225352</v>
+        <v>0.4888408927285818</v>
       </c>
     </row>
     <row r="22">
@@ -1325,35 +1365,37 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>0.3862068917003567</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>0.06653561603462374</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3543737828731537</v>
+        <v>0.6371625661849976</v>
       </c>
       <c r="F22" t="n">
-        <v>18.17750000000001</v>
+        <v>44.7641090425532</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0496969696969697</v>
+        <v>0.6739393939393939</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
       <c r="K22" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2</v>
+        <v>0.3087248322147651</v>
       </c>
       <c r="M22" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.3658536585365854</v>
       </c>
     </row>
     <row r="23">
@@ -1366,35 +1408,37 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.005830903446353156</v>
+        <v>0.1088082879388709</v>
       </c>
       <c r="D23" t="n">
-        <v>8.881898537364234e-295</v>
+        <v>2.300145208636924e-07</v>
       </c>
       <c r="E23" t="n">
-        <v>0.354942262172699</v>
+        <v>0.5175822377204895</v>
       </c>
       <c r="F23" t="n">
-        <v>18.17750000000001</v>
+        <v>27.77803225806454</v>
       </c>
       <c r="G23" t="n">
-        <v>0.03766651355075792</v>
+        <v>0.1423977951309141</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
       <c r="K23" t="n">
         <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2</v>
+        <v>0.3488372093023256</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1666666666666667</v>
       </c>
     </row>
     <row r="24">
@@ -1407,35 +1451,37 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>0.2511627857029747</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>0.02558259669607099</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3240000605583191</v>
+        <v>0.6294016242027283</v>
       </c>
       <c r="F24" t="n">
-        <v>18.17750000000001</v>
+        <v>44.19869318181821</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1259600614439324</v>
+        <v>1.096774193548387</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
       <c r="K24" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2</v>
+        <v>0.2842105263157895</v>
       </c>
       <c r="M24" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.3048128342245989</v>
       </c>
     </row>
     <row r="25">
@@ -1448,35 +1494,37 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>0.2352941137852963</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>1.777798808715947e-79</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3377845585346222</v>
+        <v>0.5950129628181458</v>
       </c>
       <c r="F25" t="n">
-        <v>18.17750000000001</v>
+        <v>52.245</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1236802413273002</v>
+        <v>0.4012066365007542</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
       <c r="K25" t="n">
         <v>0.5</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2</v>
+        <v>0.2121212121212121</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1549295774647887</v>
       </c>
     </row>
     <row r="26">
@@ -1489,35 +1537,37 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>0.2550335524255665</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>1.526247344882286e-155</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3307645320892334</v>
+        <v>0.6127455234527588</v>
       </c>
       <c r="F26" t="n">
-        <v>18.17750000000001</v>
+        <v>48.24250000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1421143847487002</v>
+        <v>0.5805892547660312</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
       <c r="K26" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
+        <v>0.2272727272727273</v>
+      </c>
+      <c r="M26" t="n">
         <v>0.2</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0.1428571428571428</v>
       </c>
     </row>
     <row r="27">
@@ -1530,35 +1580,37 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>0.2499999959820507</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>0.01362079073436029</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3288788795471191</v>
+        <v>0.5358278155326843</v>
       </c>
       <c r="F27" t="n">
-        <v>18.17750000000001</v>
+        <v>53.35593530239103</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1121751025991792</v>
+        <v>0.4322845417236662</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
       <c r="K27" t="n">
         <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>0.2</v>
+        <v>0.3181818181818182</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2424242424242424</v>
       </c>
     </row>
     <row r="28">
@@ -1571,35 +1623,37 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.2456140306049726</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>5.860576509947883e-79</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3372243940830231</v>
+        <v>0.6032034158706665</v>
       </c>
       <c r="F28" t="n">
-        <v>18.17750000000001</v>
+        <v>48.12750000000003</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1242424242424242</v>
+        <v>0.5590909090909091</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
       <c r="K28" t="n">
         <v>0.5</v>
       </c>
       <c r="L28" t="n">
-        <v>0.2</v>
+        <v>0.2826086956521739</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2857142857142857</v>
       </c>
     </row>
     <row r="29">
@@ -1612,35 +1666,37 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.2823529362456748</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>2.97772255365967e-155</v>
       </c>
       <c r="E29" t="n">
-        <v>0.3312129080295563</v>
+        <v>0.6508529186248779</v>
       </c>
       <c r="F29" t="n">
-        <v>18.17750000000001</v>
+        <v>52.74738700564976</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1423611111111111</v>
+        <v>0.828125</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
       <c r="K29" t="n">
         <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>0.2</v>
+        <v>0.3389830508474576</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="30">
@@ -1653,35 +1709,37 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.07999999788800007</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>2.086816969704057e-155</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4661099910736084</v>
+        <v>0.4730966985225677</v>
       </c>
       <c r="F30" t="n">
-        <v>18.17750000000001</v>
+        <v>31.37374269005852</v>
       </c>
       <c r="G30" t="n">
-        <v>0.82</v>
+        <v>4.48</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
-      <c r="J30" t="inlineStr"/>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
       <c r="K30" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>0.2</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="M30" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.2156862745098039</v>
       </c>
     </row>
     <row r="31">
@@ -1694,35 +1752,37 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.05517241262877529</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>1.392503783826371e-155</v>
       </c>
       <c r="E31" t="n">
-        <v>0.4586723148822784</v>
+        <v>0.4471685588359833</v>
       </c>
       <c r="F31" t="n">
-        <v>18.17750000000001</v>
+        <v>29.74105263157898</v>
       </c>
       <c r="G31" t="n">
-        <v>0.7961165048543689</v>
+        <v>8.58252427184466</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
       <c r="K31" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>0.2</v>
+        <v>0.3482142857142857</v>
       </c>
       <c r="M31" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.3415637860082305</v>
       </c>
     </row>
     <row r="32">
@@ -1735,35 +1795,37 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>0.1290322555827264</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>2.668419795632472e-155</v>
       </c>
       <c r="E32" t="n">
-        <v>0.4568907618522644</v>
+        <v>0.5000985264778137</v>
       </c>
       <c r="F32" t="n">
-        <v>18.17750000000001</v>
+        <v>42.54500000000002</v>
       </c>
       <c r="G32" t="n">
-        <v>0.82</v>
+        <v>3.12</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="n">
+        <v>1</v>
+      </c>
       <c r="K32" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="L32" t="n">
-        <v>0.2</v>
+        <v>0.2608695652173913</v>
       </c>
       <c r="M32" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.1071428571428571</v>
       </c>
     </row>
     <row r="33">
@@ -1776,35 +1838,37 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>0.1830985868706607</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>8.67426708862619e-79</v>
       </c>
       <c r="E33" t="n">
-        <v>0.4066851437091827</v>
+        <v>0.6039671301841736</v>
       </c>
       <c r="F33" t="n">
-        <v>18.17750000000001</v>
+        <v>64.40200000000002</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2271468144044321</v>
+        <v>1.484764542936288</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
       <c r="K33" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L33" t="n">
-        <v>0.2</v>
+        <v>0.3380281690140845</v>
       </c>
       <c r="M33" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.2592592592592593</v>
       </c>
     </row>
     <row r="34">
@@ -1817,35 +1881,37 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>0.1546961280583622</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>1.331703150371593e-155</v>
       </c>
       <c r="E34" t="n">
-        <v>0.387653112411499</v>
+        <v>0.5606230497360229</v>
       </c>
       <c r="F34" t="n">
-        <v>18.17750000000001</v>
+        <v>59.32328571428573</v>
       </c>
       <c r="G34" t="n">
-        <v>0.1191860465116279</v>
+        <v>0.5494186046511628</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
       <c r="K34" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>0.2</v>
+        <v>0.34</v>
       </c>
       <c r="M34" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2173913043478261</v>
       </c>
     </row>
     <row r="35">
@@ -1858,35 +1924,37 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>0.2833787416296803</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>0.06787718494567502</v>
       </c>
       <c r="E35" t="n">
-        <v>0.3536517918109894</v>
+        <v>0.6573120951652527</v>
       </c>
       <c r="F35" t="n">
-        <v>18.17750000000001</v>
+        <v>25.80440384615386</v>
       </c>
       <c r="G35" t="n">
-        <v>0.07180385288966724</v>
+        <v>0.9395796847635727</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1</v>
+      </c>
       <c r="K35" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>0.2</v>
+        <v>0.3170731707317073</v>
       </c>
       <c r="M35" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.3548387096774193</v>
       </c>
     </row>
     <row r="36">
@@ -1899,35 +1967,37 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>0.2408376916378389</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>2.673284978658312e-155</v>
       </c>
       <c r="E36" t="n">
-        <v>0.3259139358997345</v>
+        <v>0.5875635147094727</v>
       </c>
       <c r="F36" t="n">
-        <v>18.17750000000001</v>
+        <v>43.2726015037594</v>
       </c>
       <c r="G36" t="n">
-        <v>0.1299524564183835</v>
+        <v>0.820919175911252</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
       <c r="K36" t="n">
         <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>0.2</v>
+        <v>0.2698412698412698</v>
       </c>
       <c r="M36" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="37">
@@ -1940,35 +2010,37 @@
         </is>
       </c>
       <c r="C37" t="n">
+        <v>0.2139037384529155</v>
+      </c>
+      <c r="D37" t="n">
+        <v>5.974857919522055e-79</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.6419708132743835</v>
+      </c>
+      <c r="F37" t="n">
+        <v>61.02199999999999</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1.343584305408271</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" t="n">
         <v>0</v>
       </c>
-      <c r="D37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.3582238852977753</v>
-      </c>
-      <c r="F37" t="n">
-        <v>18.17750000000001</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0.08695652173913043</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="n">
-        <v>0.5</v>
-      </c>
       <c r="L37" t="n">
-        <v>0.2</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="M37" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.5192307692307693</v>
       </c>
     </row>
     <row r="38">
@@ -1981,35 +2053,37 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.2666666616801098</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>3.503348170824588e-155</v>
       </c>
       <c r="E38" t="n">
-        <v>0.3600032925605774</v>
+        <v>0.6014745831489563</v>
       </c>
       <c r="F38" t="n">
-        <v>18.17750000000001</v>
+        <v>29.37976090225567</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1060802069857697</v>
+        <v>1.14359637774903</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1</v>
+      </c>
       <c r="K38" t="n">
         <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>0.2</v>
+        <v>0.2457627118644068</v>
       </c>
       <c r="M38" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.4346289752650176</v>
       </c>
     </row>
     <row r="39">
@@ -2022,35 +2096,37 @@
         </is>
       </c>
       <c r="C39" t="n">
+        <v>0.2008733574531379</v>
+      </c>
+      <c r="D39" t="n">
+        <v>3.839245936998267e-155</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.6582720279693604</v>
+      </c>
+      <c r="F39" t="n">
+        <v>34.98882322175734</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1.269911504424779</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" t="n">
         <v>0</v>
       </c>
-      <c r="D39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0.3516546189785004</v>
-      </c>
-      <c r="F39" t="n">
-        <v>18.17750000000001</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.1209439528023599</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="n">
-        <v>1</v>
-      </c>
       <c r="L39" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="M39" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.4190871369294605</v>
       </c>
     </row>
     <row r="40">
@@ -2063,35 +2139,37 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>0.2131147494423543</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>0.01480003679540396</v>
       </c>
       <c r="E40" t="n">
-        <v>0.2961157560348511</v>
+        <v>0.5546265244483948</v>
       </c>
       <c r="F40" t="n">
-        <v>18.17750000000001</v>
+        <v>53.72872302158277</v>
       </c>
       <c r="G40" t="n">
-        <v>0.09030837004405286</v>
+        <v>0.5947136563876652</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" t="n">
         <v>1</v>
       </c>
-      <c r="J40" t="inlineStr"/>
+      <c r="J40" t="n">
+        <v>1</v>
+      </c>
       <c r="K40" t="n">
         <v>0.5</v>
       </c>
       <c r="L40" t="n">
-        <v>0.2</v>
+        <v>0.3661971830985916</v>
       </c>
       <c r="M40" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.3670886075949367</v>
       </c>
     </row>
     <row r="41">
@@ -2104,35 +2182,37 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>0.2349397554412833</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>0.001934249399250621</v>
       </c>
       <c r="E41" t="n">
-        <v>0.2989104390144348</v>
+        <v>0.6642762422561646</v>
       </c>
       <c r="F41" t="n">
-        <v>18.17750000000001</v>
+        <v>53.29224137931038</v>
       </c>
       <c r="G41" t="n">
-        <v>0.05624142661179699</v>
+        <v>0.3106995884773662</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="I41" t="n">
         <v>1</v>
       </c>
-      <c r="J41" t="inlineStr"/>
+      <c r="J41" t="n">
+        <v>1</v>
+      </c>
       <c r="K41" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L41" t="n">
-        <v>0.2</v>
+        <v>0.293103448275862</v>
       </c>
       <c r="M41" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2682926829268293</v>
       </c>
     </row>
     <row r="42">
@@ -2145,35 +2225,37 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.01265822711744917</v>
+        <v>0.3003952521201707</v>
       </c>
       <c r="D42" t="n">
-        <v>6.490056534318242e-251</v>
+        <v>0.02706927422718192</v>
       </c>
       <c r="E42" t="n">
-        <v>0.3356978297233582</v>
+        <v>0.6386897563934326</v>
       </c>
       <c r="F42" t="n">
-        <v>18.17750000000001</v>
+        <v>45.84807692307695</v>
       </c>
       <c r="G42" t="n">
-        <v>0.09371428571428571</v>
+        <v>0.64</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I42" t="n">
         <v>1</v>
       </c>
-      <c r="J42" t="inlineStr"/>
+      <c r="J42" t="n">
+        <v>1</v>
+      </c>
       <c r="K42" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L42" t="n">
-        <v>0.2</v>
+        <v>0.2763157894736842</v>
       </c>
       <c r="M42" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2660550458715596</v>
       </c>
     </row>
     <row r="43">
@@ -2186,35 +2268,37 @@
         </is>
       </c>
       <c r="C43" t="n">
+        <v>0.1687763672523991</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.01328845794961592</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.6505063772201538</v>
+      </c>
+      <c r="F43" t="n">
+        <v>33.69680000000002</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.4179796107506951</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" t="n">
         <v>0</v>
       </c>
-      <c r="D43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" t="n">
-        <v>0.362062394618988</v>
-      </c>
-      <c r="F43" t="n">
-        <v>18.17750000000001</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0.07599629286376275</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>0.2</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="M43" t="n">
-        <v>0.02564102564102564</v>
+        <v>0.1093117408906883</v>
       </c>
     </row>
     <row r="44">
@@ -2227,35 +2311,37 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>0.2307692259829189</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>0.02954706514525277</v>
       </c>
       <c r="E44" t="n">
-        <v>0.3328955769538879</v>
+        <v>0.7008967995643616</v>
       </c>
       <c r="F44" t="n">
-        <v>18.17750000000001</v>
+        <v>46.00980134538577</v>
       </c>
       <c r="G44" t="n">
-        <v>0.09414466130884042</v>
+        <v>1.812858783008037</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1</v>
+      </c>
       <c r="K44" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L44" t="n">
-        <v>0.2</v>
+        <v>0.2736842105263158</v>
       </c>
       <c r="M44" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.4164456233421751</v>
       </c>
     </row>
     <row r="45">
@@ -2268,35 +2354,37 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>0.3560606015045659</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>0.06324353063451552</v>
       </c>
       <c r="E45" t="n">
-        <v>0.36503866314888</v>
+        <v>0.6307464241981506</v>
       </c>
       <c r="F45" t="n">
-        <v>18.17750000000001</v>
+        <v>38.8847407229577</v>
       </c>
       <c r="G45" t="n">
-        <v>0.02248423361667124</v>
+        <v>0.6133808609816287</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.5</v>
+      </c>
       <c r="K45" t="n">
         <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>0.2</v>
+        <v>0.2711864406779661</v>
       </c>
       <c r="M45" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.6099290780141844</v>
       </c>
     </row>
     <row r="46">
@@ -2309,35 +2397,37 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>0.1975683862329431</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>0.0009735805746158158</v>
       </c>
       <c r="E46" t="n">
-        <v>0.3502118289470673</v>
+        <v>0.6121154427528381</v>
       </c>
       <c r="F46" t="n">
-        <v>18.17750000000001</v>
+        <v>58.51630945679707</v>
       </c>
       <c r="G46" t="n">
-        <v>0.02270839102741623</v>
+        <v>0.185267238991969</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1</v>
+      </c>
       <c r="K46" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>0.2</v>
+        <v>0.2906976744186047</v>
       </c>
       <c r="M46" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.4845360824742268</v>
       </c>
     </row>
     <row r="47">
@@ -2350,35 +2440,37 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>0.3213610545381128</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>0.0243251300372438</v>
       </c>
       <c r="E47" t="n">
-        <v>0.3643769919872284</v>
+        <v>0.6501205563545227</v>
       </c>
       <c r="F47" t="n">
-        <v>18.17750000000001</v>
+        <v>30.54264941498897</v>
       </c>
       <c r="G47" t="n">
-        <v>0.03268234356317258</v>
+        <v>0.4228776404942208</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1</v>
+      </c>
       <c r="K47" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>0.2</v>
+        <v>0.3025210084033613</v>
       </c>
       <c r="M47" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.4666666666666667</v>
       </c>
     </row>
     <row r="48">
@@ -2391,35 +2483,37 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>0.1921397335565684</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>3.009137526091424e-155</v>
       </c>
       <c r="E48" t="n">
-        <v>0.3732731342315674</v>
+        <v>0.6365370154380798</v>
       </c>
       <c r="F48" t="n">
-        <v>18.17750000000001</v>
+        <v>17.07114348302301</v>
       </c>
       <c r="G48" t="n">
-        <v>0.1755888650963597</v>
+        <v>2.137044967880086</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1</v>
+      </c>
       <c r="K48" t="n">
         <v>0.5</v>
       </c>
       <c r="L48" t="n">
-        <v>0.2</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="M48" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.3798449612403101</v>
       </c>
     </row>
     <row r="49">
@@ -2432,35 +2526,37 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>0.1884816704235083</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>0.0251064416017619</v>
       </c>
       <c r="E49" t="n">
-        <v>0.3575944304466248</v>
+        <v>0.6036085486412048</v>
       </c>
       <c r="F49" t="n">
-        <v>18.17750000000001</v>
+        <v>31.76106283422462</v>
       </c>
       <c r="G49" t="n">
-        <v>0.1579961464354528</v>
+        <v>1.310211946050096</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1</v>
+      </c>
       <c r="K49" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L49" t="n">
-        <v>0.2</v>
+        <v>0.2564102564102564</v>
       </c>
       <c r="M49" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.2982456140350877</v>
       </c>
     </row>
     <row r="50">
@@ -2473,35 +2569,37 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>0.2042553144641015</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>0.01738780587599618</v>
       </c>
       <c r="E50" t="n">
-        <v>0.3559588491916656</v>
+        <v>0.6312508583068848</v>
       </c>
       <c r="F50" t="n">
-        <v>18.17750000000001</v>
+        <v>35.99870233246949</v>
       </c>
       <c r="G50" t="n">
-        <v>0.157088122605364</v>
+        <v>1.814176245210728</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1</v>
+      </c>
       <c r="K50" t="n">
         <v>0.5</v>
       </c>
       <c r="L50" t="n">
-        <v>0.2</v>
+        <v>0.2912621359223301</v>
       </c>
       <c r="M50" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.3286219081272085</v>
       </c>
     </row>
     <row r="51">
@@ -2514,35 +2612,37 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>0.2719033185925649</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>1.043540499499188e-78</v>
       </c>
       <c r="E51" t="n">
-        <v>0.3522716164588928</v>
+        <v>0.625874936580658</v>
       </c>
       <c r="F51" t="n">
-        <v>18.17750000000001</v>
+        <v>41.32096045197741</v>
       </c>
       <c r="G51" t="n">
-        <v>0.1091877496671105</v>
+        <v>1.754993342210386</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1</v>
+      </c>
       <c r="K51" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L51" t="n">
-        <v>0.2</v>
+        <v>0.2792207792207792</v>
       </c>
       <c r="M51" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="52">
@@ -2555,35 +2655,37 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.008368200347332884</v>
+        <v>0.217765038541884</v>
       </c>
       <c r="D52" t="n">
-        <v>1.337700353554117e-259</v>
+        <v>0.0128160358684791</v>
       </c>
       <c r="E52" t="n">
-        <v>0.3636881113052368</v>
+        <v>0.59571373462677</v>
       </c>
       <c r="F52" t="n">
-        <v>18.17750000000001</v>
+        <v>44.05383869011524</v>
       </c>
       <c r="G52" t="n">
-        <v>0.05946337926033358</v>
+        <v>0.5250181290790428</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1</v>
+      </c>
       <c r="K52" t="n">
         <v>1</v>
       </c>
       <c r="L52" t="n">
-        <v>0.2</v>
+        <v>0.1844660194174757</v>
       </c>
       <c r="M52" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.3852459016393442</v>
       </c>
     </row>
     <row r="53">
@@ -2596,35 +2698,37 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>0.3625254534202198</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>0.02733090230668268</v>
       </c>
       <c r="E53" t="n">
-        <v>0.3401545286178589</v>
+        <v>0.6716035604476929</v>
       </c>
       <c r="F53" t="n">
-        <v>18.17750000000001</v>
+        <v>42.40860518190365</v>
       </c>
       <c r="G53" t="n">
-        <v>0.04375667022411953</v>
+        <v>0.6488794023479189</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1</v>
+      </c>
       <c r="K53" t="n">
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>0.2</v>
+        <v>0.270440251572327</v>
       </c>
       <c r="M53" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.4366197183098592</v>
       </c>
     </row>
     <row r="54">
@@ -2637,35 +2741,37 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>0.1124497964458638</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>4.652197395457911e-159</v>
       </c>
       <c r="E54" t="n">
-        <v>0.3295550942420959</v>
+        <v>0.5646926760673523</v>
       </c>
       <c r="F54" t="n">
-        <v>18.17750000000001</v>
+        <v>21.97300000000004</v>
       </c>
       <c r="G54" t="n">
-        <v>0.06033848417954378</v>
+        <v>0.2310522442972774</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
-      <c r="J54" t="inlineStr"/>
+      <c r="J54" t="n">
+        <v>1</v>
+      </c>
       <c r="K54" t="n">
         <v>0.5</v>
       </c>
       <c r="L54" t="n">
-        <v>0.2</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="M54" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.126984126984127</v>
       </c>
     </row>
     <row r="55">
@@ -2678,35 +2784,37 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>0.06666666441015097</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>3.80854569560441e-158</v>
       </c>
       <c r="E55" t="n">
-        <v>0.3474581241607666</v>
+        <v>0.5720757246017456</v>
       </c>
       <c r="F55" t="n">
-        <v>18.17750000000001</v>
+        <v>5.618909883720931</v>
       </c>
       <c r="G55" t="n">
-        <v>0.05304010349288486</v>
+        <v>0.2121604139715395</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1</v>
+      </c>
       <c r="K55" t="n">
         <v>0.5</v>
       </c>
       <c r="L55" t="n">
-        <v>0.2</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="M55" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.2105263157894737</v>
       </c>
     </row>
     <row r="56">
@@ -2719,35 +2827,37 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>0.1780415391397301</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>0.003004532769915607</v>
       </c>
       <c r="E56" t="n">
-        <v>0.3379605710506439</v>
+        <v>0.6103305816650391</v>
       </c>
       <c r="F56" t="n">
-        <v>18.17750000000001</v>
+        <v>27.8866727581256</v>
       </c>
       <c r="G56" t="n">
-        <v>0.05232929164007658</v>
+        <v>0.396936821952776</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>0.9047619047619048</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1</v>
+      </c>
       <c r="K56" t="n">
         <v>1</v>
       </c>
       <c r="L56" t="n">
-        <v>0.2</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="M56" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.3452380952380952</v>
       </c>
     </row>
     <row r="57">
@@ -2760,35 +2870,37 @@
         </is>
       </c>
       <c r="C57" t="n">
+        <v>0.100775191567514</v>
+      </c>
+      <c r="D57" t="n">
+        <v>8.833749696962384e-160</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.5787584781646729</v>
+      </c>
+      <c r="F57" t="n">
+        <v>6.36324193548387</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.1592005513439008</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" t="n">
         <v>0</v>
       </c>
-      <c r="D57" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" t="n">
-        <v>0.3721605241298676</v>
-      </c>
-      <c r="F57" t="n">
-        <v>18.17750000000001</v>
-      </c>
-      <c r="G57" t="n">
-        <v>0.02825637491385252</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L57" t="n">
-        <v>0.2</v>
+        <v>0.2203389830508475</v>
       </c>
       <c r="M57" t="n">
-        <v>0.04</v>
+        <v>0.1111111111111111</v>
       </c>
     </row>
     <row r="58">
@@ -2801,35 +2913,37 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0.01197604721144541</v>
+        <v>0.1791044744239004</v>
       </c>
       <c r="D58" t="n">
-        <v>7.209801557273821e-253</v>
+        <v>3.156456764334584e-157</v>
       </c>
       <c r="E58" t="n">
-        <v>0.3468083739280701</v>
+        <v>0.5300702452659607</v>
       </c>
       <c r="F58" t="n">
-        <v>18.17750000000001</v>
+        <v>23.95756410256416</v>
       </c>
       <c r="G58" t="n">
-        <v>0.08855291576673865</v>
+        <v>0.3002159827213823</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1</v>
+      </c>
       <c r="K58" t="n">
         <v>1</v>
       </c>
       <c r="L58" t="n">
-        <v>0.2</v>
+        <v>0.3125</v>
       </c>
       <c r="M58" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1764705882352941</v>
       </c>
     </row>
     <row r="59">
@@ -2842,35 +2956,37 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>0.09467455253807654</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>5.468024105341389e-233</v>
       </c>
       <c r="E59" t="n">
-        <v>0.3638429939746857</v>
+        <v>0.5583122968673706</v>
       </c>
       <c r="F59" t="n">
-        <v>18.17750000000001</v>
+        <v>7.75595785440612</v>
       </c>
       <c r="G59" t="n">
-        <v>0.1035353535353535</v>
+        <v>0.3939393939393939</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
-      <c r="J59" t="inlineStr"/>
+      <c r="J59" t="n">
+        <v>1</v>
+      </c>
       <c r="K59" t="n">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="L59" t="n">
-        <v>0.2</v>
+        <v>0.3157894736842105</v>
       </c>
       <c r="M59" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1666666666666667</v>
       </c>
     </row>
     <row r="60">
@@ -2883,35 +2999,37 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.004454342720720646</v>
+        <v>0.184501842032584</v>
       </c>
       <c r="D60" t="n">
-        <v>4.619442984542263e-300</v>
+        <v>0.0007467181732013424</v>
       </c>
       <c r="E60" t="n">
-        <v>0.3617115616798401</v>
+        <v>0.6244144439697266</v>
       </c>
       <c r="F60" t="n">
-        <v>18.17750000000001</v>
+        <v>-1.772625000000005</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0286512928022362</v>
+        <v>0.2131376659678546</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1</v>
+      </c>
       <c r="K60" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L60" t="n">
-        <v>0.2</v>
+        <v>0.2875</v>
       </c>
       <c r="M60" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.2753623188405797</v>
       </c>
     </row>
     <row r="61">
@@ -2924,35 +3042,37 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0</v>
+        <v>0.1538461511671296</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>5.21589699073297e-79</v>
       </c>
       <c r="E61" t="n">
-        <v>0.384681910276413</v>
+        <v>0.4778137505054474</v>
       </c>
       <c r="F61" t="n">
-        <v>18.17750000000001</v>
+        <v>44.61428571428573</v>
       </c>
       <c r="G61" t="n">
-        <v>0.3319838056680162</v>
+        <v>4.016194331983805</v>
       </c>
       <c r="H61" t="n">
         <v>1</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1</v>
+      </c>
       <c r="K61" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L61" t="n">
-        <v>0.2</v>
+        <v>0.2704918032786885</v>
       </c>
       <c r="M61" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.3478260869565217</v>
       </c>
     </row>
     <row r="62">
@@ -2965,35 +3085,37 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>0.1954022939800504</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>7.063788090273745e-79</v>
       </c>
       <c r="E62" t="n">
-        <v>0.3322982490062714</v>
+        <v>0.632626473903656</v>
       </c>
       <c r="F62" t="n">
-        <v>18.17750000000001</v>
+        <v>42.91264214046828</v>
       </c>
       <c r="G62" t="n">
-        <v>0.205</v>
+        <v>1.6825</v>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1</v>
+      </c>
       <c r="K62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" t="n">
-        <v>0.2</v>
+        <v>0.2891566265060241</v>
       </c>
       <c r="M62" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.3467336683417085</v>
       </c>
     </row>
     <row r="63">
@@ -3006,35 +3128,37 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>0.2445414798466849</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>3.124656596953237e-155</v>
       </c>
       <c r="E63" t="n">
-        <v>0.3240036368370056</v>
+        <v>0.6403332948684692</v>
       </c>
       <c r="F63" t="n">
-        <v>18.17750000000001</v>
+        <v>60.93000000000004</v>
       </c>
       <c r="G63" t="n">
-        <v>0.1143654114365411</v>
+        <v>0.8633193863319386</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1</v>
+      </c>
       <c r="K63" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L63" t="n">
-        <v>0.2</v>
+        <v>0.4324324324324325</v>
       </c>
       <c r="M63" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.2753623188405797</v>
       </c>
     </row>
     <row r="64">
@@ -3047,35 +3171,37 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>0.2753036387844417</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>4.316577219300353e-155</v>
       </c>
       <c r="E64" t="n">
-        <v>0.3228385746479034</v>
+        <v>0.6672869324684143</v>
       </c>
       <c r="F64" t="n">
-        <v>18.17750000000001</v>
+        <v>56.20788927335641</v>
       </c>
       <c r="G64" t="n">
-        <v>0.1344262295081967</v>
+        <v>1.431147540983607</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1</v>
+      </c>
       <c r="K64" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L64" t="n">
-        <v>0.2</v>
+        <v>0.3425925925925926</v>
       </c>
       <c r="M64" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.3636363636363636</v>
       </c>
     </row>
     <row r="65">
@@ -3088,35 +3214,37 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>0</v>
+        <v>0.2762430889301304</v>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>9.780277285639061e-79</v>
       </c>
       <c r="E65" t="n">
-        <v>0.3265484273433685</v>
+        <v>0.6209030747413635</v>
       </c>
       <c r="F65" t="n">
-        <v>18.17750000000001</v>
+        <v>35.98593023255816</v>
       </c>
       <c r="G65" t="n">
-        <v>0.1643286573146293</v>
+        <v>1.158316633266533</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J65" t="n">
+        <v>1</v>
+      </c>
       <c r="K65" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L65" t="n">
-        <v>0.2</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M65" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.3529411764705883</v>
       </c>
     </row>
     <row r="66">
@@ -3129,35 +3257,37 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0</v>
+        <v>0.298136640995332</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>0.0571884361243411</v>
       </c>
       <c r="E66" t="n">
-        <v>0.3350982666015625</v>
+        <v>0.714253842830658</v>
       </c>
       <c r="F66" t="n">
-        <v>18.17750000000001</v>
+        <v>40.53819964349378</v>
       </c>
       <c r="G66" t="n">
-        <v>0.1028858218318695</v>
+        <v>1.409033877038896</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J66" t="n">
+        <v>1</v>
+      </c>
       <c r="K66" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L66" t="n">
-        <v>0.2</v>
+        <v>0.3306451612903226</v>
       </c>
       <c r="M66" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.4642857142857143</v>
       </c>
     </row>
     <row r="67">
@@ -3170,35 +3300,37 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>0.2166064932236835</v>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>3.084116923537544e-155</v>
       </c>
       <c r="E67" t="n">
-        <v>0.3333593308925629</v>
+        <v>0.6865761280059814</v>
       </c>
       <c r="F67" t="n">
-        <v>18.17750000000001</v>
+        <v>41.6782156019656</v>
       </c>
       <c r="G67" t="n">
-        <v>0.1123287671232877</v>
+        <v>1.305479452054795</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J67" t="n">
+        <v>1</v>
+      </c>
       <c r="K67" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L67" t="n">
-        <v>0.2</v>
+        <v>0.287037037037037</v>
       </c>
       <c r="M67" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.3893129770992366</v>
       </c>
     </row>
     <row r="68">
@@ -3211,35 +3343,37 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>0.05882352864179703</v>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>6.577771803681657e-232</v>
       </c>
       <c r="E68" t="n">
-        <v>0.4337139129638672</v>
+        <v>0.4336404800415039</v>
       </c>
       <c r="F68" t="n">
-        <v>18.17750000000001</v>
+        <v>22.42743968208916</v>
       </c>
       <c r="G68" t="n">
-        <v>0.6456692913385826</v>
+        <v>19.34645669291339</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J68" t="n">
+        <v>1</v>
+      </c>
       <c r="K68" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L68" t="n">
-        <v>0.2</v>
+        <v>0.2388059701492537</v>
       </c>
       <c r="M68" t="n">
-        <v>0.2</v>
+        <v>0.7324414715719063</v>
       </c>
     </row>
   </sheetData>
